--- a/tabs/ZDATA_map_I_have_been.xlsx
+++ b/tabs/ZDATA_map_I_have_been.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e64a25058d50c5c4/OneD-2025/6_homepage_byungkiryu/byungkiryu/tabs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e64a25058d50c5c4/OneD-2026/6_homepage_byungkiryu/byungkiryu/tabs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="323" documentId="13_ncr:1_{4AE1A52B-229F-42E3-9DC6-6ED5CB8C9B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FDA76D5-1F59-4D6C-A1C5-7C8F99666DE8}"/>
+  <xr:revisionPtr revIDLastSave="378" documentId="13_ncr:1_{4AE1A52B-229F-42E3-9DC6-6ED5CB8C9B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1C557C6-9F60-4507-A30A-126859416820}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="read" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="236">
   <si>
     <t>site</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -932,6 +932,54 @@
   </si>
   <si>
     <t>Sendai</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hukuoka</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hita</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Denver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Honolulu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[MRS]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ICT]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold Coast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Austrailia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[PRICM-12]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Edingburgh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ECT]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[MS&amp;T26]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1152,327 +1200,6 @@
   </cellStyles>
   <dxfs count="34">
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="0.00000"/>
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="0.00000"/>
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="176" formatCode="yyyy/mmm"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1733,6 +1460,324 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="0.00000"/>
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="0.00000"/>
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="176" formatCode="yyyy/mmm"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="thin">
           <color indexed="64"/>
@@ -1754,6 +1799,9 @@
           <color indexed="64"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -1787,47 +1835,43 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{773460B6-1672-4C3D-AA63-31731A2ED31A}" name="표1" displayName="표1" ref="A1:L84" totalsRowShown="0" headerRowDxfId="33" dataDxfId="12" headerRowBorderDxfId="32" tableBorderDxfId="31" totalsRowBorderDxfId="30">
-  <autoFilter ref="A1:L84" xr:uid="{773460B6-1672-4C3D-AA63-31731A2ED31A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{773460B6-1672-4C3D-AA63-31731A2ED31A}" name="표1" displayName="표1" ref="A1:L92" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
+  <autoFilter ref="A1:L92" xr:uid="{773460B6-1672-4C3D-AA63-31731A2ED31A}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{03AA161E-E864-4331-AC14-B9C9DAF075CA}" name="num" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{2E31BAC7-B3B9-4D60-96FD-1B77E2C90E7E}" name="when" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{0896C7E6-5200-4BDA-B0C8-48F74A992022}" name="date_started" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{D79B4E10-3077-40F6-B6E9-26EB2062EB3C}" name="date_ended" dataDxfId="8"/>
-    <tableColumn id="16" xr3:uid="{22A80980-023F-4F33-A32E-EF45372AEADA}" name="site" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{40AD35C2-3494-4CCA-8424-8F12DCD25076}" name="city" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{A8ADD25B-4109-4AF6-9AD6-906F4B09F5EF}" name="country" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{618D45E6-8E9F-4182-86CB-E4FF4C867771}" name="type" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{A5525C00-D1A9-402F-B174-CFFEE4388915}" name="contents" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{055048FB-1799-4726-9A21-F7EF88B0C66E}" name="radius" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{6CF118A3-8975-446A-A427-93C39E0AD2EC}" name="latitude" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{353CBE02-EDA6-41BD-B979-FD2FB9CF6BED}" name="longitude" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{03AA161E-E864-4331-AC14-B9C9DAF075CA}" name="num" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{2E31BAC7-B3B9-4D60-96FD-1B77E2C90E7E}" name="when" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{0896C7E6-5200-4BDA-B0C8-48F74A992022}" name="date_started" dataDxfId="26"/>
+    <tableColumn id="12" xr3:uid="{D79B4E10-3077-40F6-B6E9-26EB2062EB3C}" name="date_ended" dataDxfId="25"/>
+    <tableColumn id="16" xr3:uid="{22A80980-023F-4F33-A32E-EF45372AEADA}" name="site" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{40AD35C2-3494-4CCA-8424-8F12DCD25076}" name="city" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{A8ADD25B-4109-4AF6-9AD6-906F4B09F5EF}" name="country" dataDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{618D45E6-8E9F-4182-86CB-E4FF4C867771}" name="type" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{A5525C00-D1A9-402F-B174-CFFEE4388915}" name="contents" dataDxfId="20"/>
+    <tableColumn id="15" xr3:uid="{055048FB-1799-4726-9A21-F7EF88B0C66E}" name="radius" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{6CF118A3-8975-446A-A427-93C39E0AD2EC}" name="latitude" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{353CBE02-EDA6-41BD-B979-FD2FB9CF6BED}" name="longitude" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6A8D1F5B-4E52-4615-91B1-7B363AE7B378}" name="표1_3" displayName="표1_3" ref="A1:L56" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26" totalsRowBorderDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6A8D1F5B-4E52-4615-91B1-7B363AE7B378}" name="표1_3" displayName="표1_3" ref="A1:L56" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
   <autoFilter ref="A1:L56" xr:uid="{773460B6-1672-4C3D-AA63-31731A2ED31A}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{78338D92-4A2B-4E3D-B156-5393467C4061}" name="num" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{B3383091-E12B-43EF-ACAC-A5EB5A892701}" name="when" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{34A24A59-DBBD-418A-B541-86DDB6AF48F5}" name="date_started" dataDxfId="22"/>
-    <tableColumn id="12" xr3:uid="{B7D59EC0-301C-49AE-95B6-CC932F436792}" name="date_ended" dataDxfId="21"/>
-    <tableColumn id="16" xr3:uid="{6E0111C9-A727-4005-8C09-F6964EF90082}" name="site" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{66936F99-D07A-4478-941D-2619729812E2}" name="city" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{FDC90E21-419E-43E6-AC89-42FD322D1A5D}" name="country" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{DB3DDC50-71EA-48E0-9BF6-65B4CB489E96}" name="type" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{BD1BFF4B-CD7F-4FCB-A2F7-E3D8577FF561}" name="contents" dataDxfId="16"/>
-    <tableColumn id="15" xr3:uid="{0CD3D8B2-7F8E-4996-B2BD-5A8501031FC9}" name="radius" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{D5694425-F33F-40F5-A0DA-4C2A2E220D0B}" name="latitude" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{D4104559-BC0B-4315-B4AB-4C36A9898C10}" name="longitude" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{78338D92-4A2B-4E3D-B156-5393467C4061}" name="num" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{B3383091-E12B-43EF-ACAC-A5EB5A892701}" name="when" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{34A24A59-DBBD-418A-B541-86DDB6AF48F5}" name="date_started" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{B7D59EC0-301C-49AE-95B6-CC932F436792}" name="date_ended" dataDxfId="8"/>
+    <tableColumn id="16" xr3:uid="{6E0111C9-A727-4005-8C09-F6964EF90082}" name="site" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{66936F99-D07A-4478-941D-2619729812E2}" name="city" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{FDC90E21-419E-43E6-AC89-42FD322D1A5D}" name="country" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{DB3DDC50-71EA-48E0-9BF6-65B4CB489E96}" name="type" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{BD1BFF4B-CD7F-4FCB-A2F7-E3D8577FF561}" name="contents" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{0CD3D8B2-7F8E-4996-B2BD-5A8501031FC9}" name="radius" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{D5694425-F33F-40F5-A0DA-4C2A2E220D0B}" name="latitude" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{D4104559-BC0B-4315-B4AB-4C36A9898C10}" name="longitude" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2096,23 +2140,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039E1221-B957-4248-8270-E37652A544F1}">
-  <dimension ref="A1:L84"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <dimension ref="A1:L92"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="7.0625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.4375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.8125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1875" customWidth="1"/>
+    <col min="1" max="1" width="7.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.4140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1640625" customWidth="1"/>
     <col min="6" max="7" width="16.5" customWidth="1"/>
-    <col min="8" max="8" width="12.1875" customWidth="1"/>
-    <col min="9" max="9" width="41.3125" customWidth="1"/>
-    <col min="10" max="10" width="10.5625" customWidth="1"/>
+    <col min="8" max="8" width="12.1640625" customWidth="1"/>
+    <col min="9" max="9" width="41.33203125" customWidth="1"/>
+    <col min="10" max="10" width="10.58203125" customWidth="1"/>
     <col min="11" max="11" width="11.75" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>57</v>
       </c>
@@ -2150,7 +2194,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="13">
         <v>-100</v>
       </c>
@@ -2180,7 +2224,7 @@
         <v>127.21859000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="13">
         <v>-10</v>
       </c>
@@ -2210,7 +2254,7 @@
         <v>128.718154</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" s="13">
         <v>1</v>
       </c>
@@ -2242,7 +2286,7 @@
         <v>-106.638927</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="13">
         <v>2</v>
       </c>
@@ -2274,7 +2318,7 @@
         <v>132.45434</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" s="13">
         <v>3</v>
       </c>
@@ -2306,7 +2350,7 @@
         <v>3.87502932513372</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="13">
         <v>4</v>
       </c>
@@ -2338,7 +2382,7 @@
         <v>120.36963815813201</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="13">
         <v>5</v>
       </c>
@@ -2370,7 +2414,7 @@
         <v>-79.996414734112406</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="13">
         <v>6</v>
       </c>
@@ -2402,7 +2446,7 @@
         <v>30.354790004319799</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="13">
         <v>7</v>
       </c>
@@ -2434,7 +2478,7 @@
         <v>116.304608750865</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="13">
         <v>8</v>
       </c>
@@ -2466,7 +2510,7 @@
         <v>-122.66329917549101</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" s="13">
         <v>9</v>
       </c>
@@ -2496,7 +2540,7 @@
         <v>135.50048238661799</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" s="13">
         <v>10</v>
       </c>
@@ -2526,7 +2570,7 @@
         <v>-9.1421650205076492</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" s="13">
         <v>10</v>
       </c>
@@ -2556,7 +2600,7 @@
         <v>-3.7029134733882998</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" s="13">
         <v>10</v>
       </c>
@@ -2586,7 +2630,7 @@
         <v>-6.0000941618518597</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" s="13">
         <v>10</v>
       </c>
@@ -2616,7 +2660,7 @@
         <v>-5.1613255266614697</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" s="13">
         <v>10</v>
       </c>
@@ -2646,7 +2690,7 @@
         <v>-4.5589643117021899</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" s="13">
         <v>10</v>
       </c>
@@ -2676,7 +2720,7 @@
         <v>-3.8708370172469202</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" s="13">
         <v>10</v>
       </c>
@@ -2706,7 +2750,7 @@
         <v>-3.6011831922437598</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" s="13">
         <v>10</v>
       </c>
@@ -2736,7 +2780,7 @@
         <v>2.1513963451336302</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" s="13">
         <v>10</v>
       </c>
@@ -2766,7 +2810,7 @@
         <v>4.89049657231672</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" s="13">
         <v>11</v>
       </c>
@@ -2796,7 +2840,7 @@
         <v>-76.616426601988394</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="31.5" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:12" ht="32" x14ac:dyDescent="0.45">
       <c r="A23" s="13">
         <v>12</v>
       </c>
@@ -2826,7 +2870,7 @@
         <v>10.5244507051922</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="31.5" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:12" ht="32" x14ac:dyDescent="0.45">
       <c r="A24" s="13">
         <v>12</v>
       </c>
@@ -2856,7 +2900,7 @@
         <v>13.4117469588773</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="31.5" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:12" ht="32" x14ac:dyDescent="0.45">
       <c r="A25" s="13">
         <v>12</v>
       </c>
@@ -2886,7 +2930,7 @@
         <v>19.9396327920016</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="31.5" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:12" ht="32" x14ac:dyDescent="0.45">
       <c r="A26" s="13">
         <v>12</v>
       </c>
@@ -2916,7 +2960,7 @@
         <v>20.996193258919099</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" s="13">
         <v>13</v>
       </c>
@@ -2946,7 +2990,7 @@
         <v>-98.484032793654407</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="31.5" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:12" ht="32" x14ac:dyDescent="0.45">
       <c r="A28" s="13">
         <v>14</v>
       </c>
@@ -2976,7 +3020,7 @@
         <v>-95.358728560659003</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="31.5" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:12" ht="32" x14ac:dyDescent="0.45">
       <c r="A29" s="13">
         <v>14</v>
       </c>
@@ -3006,7 +3050,7 @@
         <v>-122.274208076652</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="47.25" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:12" ht="48" x14ac:dyDescent="0.45">
       <c r="A30" s="13">
         <v>15</v>
       </c>
@@ -3036,7 +3080,7 @@
         <v>-76.616426601988394</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="50.65" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:12" ht="51" x14ac:dyDescent="0.45">
       <c r="A31" s="13">
         <v>15</v>
       </c>
@@ -3068,7 +3112,7 @@
         <v>-84.514263007525102</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A32" s="13">
         <v>16</v>
       </c>
@@ -3098,7 +3142,7 @@
         <v>15.9522463919101</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A33" s="13">
         <v>16</v>
       </c>
@@ -3128,7 +3172,7 @@
         <v>14.093960105654601</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A34" s="13">
         <v>16</v>
       </c>
@@ -3160,7 +3204,7 @@
         <v>14.2041002768187</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A35" s="13">
         <v>16</v>
       </c>
@@ -3190,7 +3234,7 @@
         <v>15.6189141890504</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A36" s="13">
         <v>16</v>
       </c>
@@ -3220,7 +3264,7 @@
         <v>15.220037549492901</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A37" s="13">
         <v>16</v>
       </c>
@@ -3250,7 +3294,7 @@
         <v>16.441262946199998</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:12" ht="34" x14ac:dyDescent="0.45">
       <c r="A38" s="13">
         <v>16</v>
       </c>
@@ -3280,7 +3324,7 @@
         <v>17.815059540440899</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A39" s="13">
         <v>16</v>
       </c>
@@ -3310,7 +3354,7 @@
         <v>18.107255468449399</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A40" s="13">
         <v>17</v>
       </c>
@@ -3340,7 +3384,7 @@
         <v>127.878045254618</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A41" s="13">
         <v>18</v>
       </c>
@@ -3370,7 +3414,7 @@
         <v>-90.075875256094093</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A42" s="13">
         <v>19</v>
       </c>
@@ -3400,7 +3444,7 @@
         <v>98.3067130312578</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="31.5" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:12" ht="32" x14ac:dyDescent="0.45">
       <c r="A43" s="13">
         <v>20</v>
       </c>
@@ -3430,7 +3474,7 @@
         <v>14.5639120221503</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="31.5" x14ac:dyDescent="0.6">
+    <row r="44" spans="1:12" ht="32" x14ac:dyDescent="0.45">
       <c r="A44" s="13">
         <v>20</v>
       </c>
@@ -3460,7 +3504,7 @@
         <v>11.878060676424001</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A45" s="13">
         <v>21</v>
       </c>
@@ -3490,7 +3534,7 @@
         <v>-118.268156294997</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="31.5" x14ac:dyDescent="0.6">
+    <row r="46" spans="1:12" ht="32" x14ac:dyDescent="0.45">
       <c r="A46" s="13">
         <v>22</v>
       </c>
@@ -3520,7 +3564,7 @@
         <v>-0.37014065563777399</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="31.5" x14ac:dyDescent="0.6">
+    <row r="47" spans="1:12" ht="32" x14ac:dyDescent="0.45">
       <c r="A47" s="13">
         <v>22</v>
       </c>
@@ -3552,7 +3596,7 @@
         <v>6.9584788315311696</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="47.25" x14ac:dyDescent="0.6">
+    <row r="48" spans="1:12" ht="48" x14ac:dyDescent="0.45">
       <c r="A48" s="13">
         <v>23</v>
       </c>
@@ -3582,7 +3626,7 @@
         <v>139.95252829063199</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A49" s="13">
         <v>24</v>
       </c>
@@ -3612,7 +3656,7 @@
         <v>-71.047000911793504</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="78.75" x14ac:dyDescent="0.6">
+    <row r="50" spans="1:12" ht="80" x14ac:dyDescent="0.45">
       <c r="A50" s="13">
         <v>25</v>
       </c>
@@ -3648,7 +3692,7 @@
         <v>6.9584788315311696</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="78.75" x14ac:dyDescent="0.6">
+    <row r="51" spans="1:12" ht="80" x14ac:dyDescent="0.45">
       <c r="A51" s="13">
         <v>25</v>
       </c>
@@ -3684,7 +3728,7 @@
         <v>-1.56708361785728</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="52" spans="1:12" ht="34" x14ac:dyDescent="0.45">
       <c r="A52" s="13">
         <v>26</v>
       </c>
@@ -3720,7 +3764,7 @@
         <v>-21.0368082495424</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A53" s="13">
         <v>26</v>
       </c>
@@ -3756,7 +3800,7 @@
         <v>-21.074215656130999</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A54" s="13">
         <v>26</v>
       </c>
@@ -3792,7 +3836,7 @@
         <v>-16.880123646411899</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A55" s="13">
         <v>26</v>
       </c>
@@ -3828,7 +3872,7 @@
         <v>-14.2871601973726</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A56" s="13">
         <v>26</v>
       </c>
@@ -3864,7 +3908,7 @@
         <v>-16.3690028274948</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A57" s="13">
         <v>26</v>
       </c>
@@ -3898,7 +3942,7 @@
         <v>-18.200972887932299</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A58" s="13">
         <v>26</v>
       </c>
@@ -3934,7 +3978,7 @@
         <v>-20.280849780182901</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A59" s="13">
         <v>26</v>
       </c>
@@ -3970,7 +4014,7 @@
         <v>-23.313317346255399</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A60" s="13">
         <v>26</v>
       </c>
@@ -4006,7 +4050,7 @@
         <v>-21.919546606429801</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A61" s="13">
         <v>26</v>
       </c>
@@ -4042,7 +4086,7 @@
         <v>-22.534168857815999</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A62" s="13">
         <v>26</v>
       </c>
@@ -4078,7 +4122,7 @@
         <v>24.988094</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A63" s="13">
         <v>27</v>
       </c>
@@ -4112,7 +4156,7 @@
         <v>-115.171454290643</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="31.5" x14ac:dyDescent="0.6">
+    <row r="64" spans="1:12" ht="32" x14ac:dyDescent="0.45">
       <c r="A64" s="13">
         <v>28</v>
       </c>
@@ -4146,7 +4190,7 @@
         <v>-122.337190818217</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A65" s="13">
         <v>29</v>
       </c>
@@ -4180,7 +4224,7 @@
         <v>139.76960756174401</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="31.5" x14ac:dyDescent="0.6">
+    <row r="66" spans="1:12" ht="32" x14ac:dyDescent="0.45">
       <c r="A66" s="13">
         <v>30</v>
       </c>
@@ -4214,7 +4258,7 @@
         <v>14.3797258889237</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="47.25" x14ac:dyDescent="0.6">
+    <row r="67" spans="1:12" ht="48" x14ac:dyDescent="0.45">
       <c r="A67" s="13">
         <v>31</v>
       </c>
@@ -4250,7 +4294,7 @@
         <v>140.08150225832199</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="47.25" x14ac:dyDescent="0.6">
+    <row r="68" spans="1:12" ht="48" x14ac:dyDescent="0.45">
       <c r="A68" s="13">
         <v>31</v>
       </c>
@@ -4284,7 +4328,7 @@
         <v>140.387044968476</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="47.25" x14ac:dyDescent="0.6">
+    <row r="69" spans="1:12" ht="48" x14ac:dyDescent="0.45">
       <c r="A69" s="13">
         <v>31</v>
       </c>
@@ -4318,7 +4362,7 @@
         <v>141.009338901935</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="31.5" x14ac:dyDescent="0.6">
+    <row r="70" spans="1:12" ht="32" x14ac:dyDescent="0.45">
       <c r="A70" s="13">
         <v>32</v>
       </c>
@@ -4350,7 +4394,7 @@
         <v>135.75103821800599</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A71" s="13">
         <v>33</v>
       </c>
@@ -4380,7 +4424,7 @@
         <v>-93.273939580476195</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A72" s="13">
         <v>34</v>
       </c>
@@ -4410,7 +4454,7 @@
         <v>19.9396327920016</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="47.25" x14ac:dyDescent="0.6">
+    <row r="73" spans="1:12" ht="48" x14ac:dyDescent="0.45">
       <c r="A73" s="13">
         <v>35</v>
       </c>
@@ -4440,7 +4484,7 @@
         <v>-0.17396384277622601</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="47.25" x14ac:dyDescent="0.6">
+    <row r="74" spans="1:12" ht="48" x14ac:dyDescent="0.45">
       <c r="A74" s="13">
         <v>35</v>
       </c>
@@ -4470,7 +4514,7 @@
         <v>2.3554740356442401</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="47.25" x14ac:dyDescent="0.6">
+    <row r="75" spans="1:12" ht="48" x14ac:dyDescent="0.45">
       <c r="A75" s="13">
         <v>35</v>
       </c>
@@ -4502,7 +4546,7 @@
         <v>8.3104007332115302</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="47.25" x14ac:dyDescent="0.6">
+    <row r="76" spans="1:12" ht="48" x14ac:dyDescent="0.45">
       <c r="A76" s="13">
         <v>35</v>
       </c>
@@ -4532,7 +4576,7 @@
         <v>9.2053669288753692</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="47.25" x14ac:dyDescent="0.6">
+    <row r="77" spans="1:12" ht="48" x14ac:dyDescent="0.45">
       <c r="A77" s="13">
         <v>35</v>
       </c>
@@ -4562,7 +4606,7 @@
         <v>12.326648478205801</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="47.25" x14ac:dyDescent="0.6">
+    <row r="78" spans="1:12" ht="48" x14ac:dyDescent="0.45">
       <c r="A78" s="13">
         <v>35</v>
       </c>
@@ -4592,7 +4636,7 @@
         <v>10.396707802333101</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="47.25" x14ac:dyDescent="0.6">
+    <row r="79" spans="1:12" ht="48" x14ac:dyDescent="0.45">
       <c r="A79" s="13">
         <v>35</v>
       </c>
@@ -4622,7 +4666,7 @@
         <v>11.2503227216075</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="47.25" x14ac:dyDescent="0.6">
+    <row r="80" spans="1:12" ht="48" x14ac:dyDescent="0.45">
       <c r="A80" s="13">
         <v>35</v>
       </c>
@@ -4652,7 +4696,7 @@
         <v>12.506589131448299</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="47.25" x14ac:dyDescent="0.6">
+    <row r="81" spans="1:12" ht="48" x14ac:dyDescent="0.45">
       <c r="A81" s="13">
         <v>35</v>
       </c>
@@ -4684,7 +4728,7 @@
         <v>54.485478514154103</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A82" s="13">
         <v>36</v>
       </c>
@@ -4714,7 +4758,7 @@
         <v>-117.914611697654</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A83" s="19">
         <v>37</v>
       </c>
@@ -4727,7 +4771,9 @@
       <c r="F83" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="G83" s="6"/>
+      <c r="G83" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="H83" s="5" t="s">
         <v>51</v>
       </c>
@@ -4736,7 +4782,7 @@
       <c r="K83" s="22"/>
       <c r="L83" s="22"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A84" s="19">
         <v>38</v>
       </c>
@@ -4749,7 +4795,9 @@
       <c r="F84" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="G84" s="6"/>
+      <c r="G84" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="H84" s="5" t="s">
         <v>100</v>
       </c>
@@ -4757,6 +4805,210 @@
       <c r="J84" s="6"/>
       <c r="K84" s="22"/>
       <c r="L84" s="22"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A85" s="19">
+        <v>39</v>
+      </c>
+      <c r="B85" s="8">
+        <v>45870</v>
+      </c>
+      <c r="C85" s="20"/>
+      <c r="D85" s="20"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I85" s="21"/>
+      <c r="J85" s="6"/>
+      <c r="K85" s="22"/>
+      <c r="L85" s="22"/>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A86" s="19">
+        <v>39</v>
+      </c>
+      <c r="B86" s="8">
+        <v>45870</v>
+      </c>
+      <c r="C86" s="20"/>
+      <c r="D86" s="20"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I86" s="21"/>
+      <c r="J86" s="6"/>
+      <c r="K86" s="22"/>
+      <c r="L86" s="22"/>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A87" s="19">
+        <v>40</v>
+      </c>
+      <c r="B87" s="8">
+        <v>46082</v>
+      </c>
+      <c r="C87" s="20"/>
+      <c r="D87" s="20"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H87" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I87" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="J87" s="6"/>
+      <c r="K87" s="22"/>
+      <c r="L87" s="22"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A88" s="19">
+        <v>41</v>
+      </c>
+      <c r="B88" s="8">
+        <v>46138</v>
+      </c>
+      <c r="C88" s="20"/>
+      <c r="D88" s="20"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I88" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="J88" s="6"/>
+      <c r="K88" s="22"/>
+      <c r="L88" s="22"/>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A89" s="19">
+        <v>42</v>
+      </c>
+      <c r="B89" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C89" s="20"/>
+      <c r="D89" s="20"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I89" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="J89" s="6"/>
+      <c r="K89" s="22"/>
+      <c r="L89" s="22"/>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A90" s="19">
+        <v>43</v>
+      </c>
+      <c r="B90" s="8">
+        <v>46235</v>
+      </c>
+      <c r="C90" s="20"/>
+      <c r="D90" s="20"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I90" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="J90" s="6"/>
+      <c r="K90" s="22"/>
+      <c r="L90" s="22"/>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A91" s="19">
+        <v>44</v>
+      </c>
+      <c r="B91" s="8">
+        <v>46266</v>
+      </c>
+      <c r="C91" s="20"/>
+      <c r="D91" s="20"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I91" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="J91" s="6"/>
+      <c r="K91" s="22"/>
+      <c r="L91" s="22"/>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A92" s="19">
+        <v>45</v>
+      </c>
+      <c r="B92" s="8">
+        <v>46296</v>
+      </c>
+      <c r="C92" s="20"/>
+      <c r="D92" s="20"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I92" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="J92" s="6"/>
+      <c r="K92" s="22"/>
+      <c r="L92" s="22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4771,22 +5023,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72DFFF01-404B-4EE2-ADAA-AA7281B7811D}">
   <dimension ref="A1:L56"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="7.0625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.4375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.8125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1875" customWidth="1"/>
+    <col min="1" max="1" width="7.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.4140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1640625" customWidth="1"/>
     <col min="6" max="7" width="16.5" customWidth="1"/>
-    <col min="8" max="8" width="12.1875" customWidth="1"/>
-    <col min="9" max="9" width="24.4375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5625" customWidth="1"/>
+    <col min="8" max="8" width="12.1640625" customWidth="1"/>
+    <col min="9" max="9" width="24.4140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.58203125" customWidth="1"/>
     <col min="11" max="11" width="11.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>57</v>
       </c>
@@ -4824,7 +5076,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="10">
         <v>-100</v>
       </c>
@@ -4852,7 +5104,7 @@
         <v>127.21859000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="10">
         <v>-10</v>
       </c>
@@ -4882,7 +5134,7 @@
         <v>128.718154</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" s="10">
         <v>1</v>
       </c>
@@ -4914,7 +5166,7 @@
         <v>-106.638927</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="10">
         <v>2</v>
       </c>
@@ -4946,7 +5198,7 @@
         <v>132.45434</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" s="10">
         <v>3</v>
       </c>
@@ -4978,7 +5230,7 @@
         <v>3.87502932513372</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="10">
         <v>4</v>
       </c>
@@ -5010,7 +5262,7 @@
         <v>120.36963815813201</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="10">
         <v>5</v>
       </c>
@@ -5042,7 +5294,7 @@
         <v>-79.996414734112406</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="10">
         <v>6</v>
       </c>
@@ -5074,7 +5326,7 @@
         <v>30.354790004319799</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="10">
         <v>7</v>
       </c>
@@ -5106,7 +5358,7 @@
         <v>116.304608750865</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="10">
         <v>8</v>
       </c>
@@ -5138,7 +5390,7 @@
         <v>-122.66329917549101</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" s="10">
         <v>9</v>
       </c>
@@ -5166,7 +5418,7 @@
         <v>135.50048238661799</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" s="10">
         <v>10</v>
       </c>
@@ -5196,7 +5448,7 @@
         <v>-9.1421650205076492</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" s="10">
         <v>10</v>
       </c>
@@ -5226,7 +5478,7 @@
         <v>-3.7029134733882998</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" s="10">
         <v>10</v>
       </c>
@@ -5256,7 +5508,7 @@
         <v>-6.0000941618518597</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" s="10">
         <v>10</v>
       </c>
@@ -5286,7 +5538,7 @@
         <v>-5.1613255266614697</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" s="10">
         <v>10</v>
       </c>
@@ -5316,7 +5568,7 @@
         <v>-4.5589643117021899</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" s="10">
         <v>10</v>
       </c>
@@ -5346,7 +5598,7 @@
         <v>-3.8708370172469202</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" s="10">
         <v>10</v>
       </c>
@@ -5376,7 +5628,7 @@
         <v>-3.6011831922437598</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" s="10">
         <v>10</v>
       </c>
@@ -5406,7 +5658,7 @@
         <v>2.1513963451336302</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" s="10">
         <v>10</v>
       </c>
@@ -5436,7 +5688,7 @@
         <v>4.89049657231672</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" s="10"/>
       <c r="B22" s="7"/>
       <c r="C22" s="5"/>
@@ -5450,7 +5702,7 @@
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23" s="10"/>
       <c r="B23" s="7"/>
       <c r="C23" s="5"/>
@@ -5464,7 +5716,7 @@
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24" s="10"/>
       <c r="B24" s="7"/>
       <c r="C24" s="5"/>
@@ -5478,7 +5730,7 @@
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" s="10"/>
       <c r="B25" s="7"/>
       <c r="C25" s="5"/>
@@ -5492,7 +5744,7 @@
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26" s="10"/>
       <c r="B26" s="7"/>
       <c r="C26" s="5"/>
@@ -5506,7 +5758,7 @@
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" s="10"/>
       <c r="B27" s="7"/>
       <c r="C27" s="5"/>
@@ -5520,7 +5772,7 @@
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A28" s="10"/>
       <c r="B28" s="7"/>
       <c r="C28" s="5"/>
@@ -5533,7 +5785,7 @@
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A29" s="10"/>
       <c r="B29" s="7"/>
       <c r="C29" s="5"/>
@@ -5546,7 +5798,7 @@
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A30" s="10"/>
       <c r="B30" s="7"/>
       <c r="C30" s="5"/>
@@ -5559,7 +5811,7 @@
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A31" s="10"/>
       <c r="B31" s="7"/>
       <c r="C31" s="5"/>
@@ -5572,7 +5824,7 @@
       <c r="K31" s="5"/>
       <c r="L31" s="5"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A32" s="10"/>
       <c r="B32" s="7"/>
       <c r="C32" s="5"/>
@@ -5585,7 +5837,7 @@
       <c r="K32" s="5"/>
       <c r="L32" s="5"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A33" s="10"/>
       <c r="B33" s="7"/>
       <c r="C33" s="5"/>
@@ -5598,7 +5850,7 @@
       <c r="K33" s="5"/>
       <c r="L33" s="5"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A34" s="10"/>
       <c r="B34" s="7"/>
       <c r="C34" s="5"/>
@@ -5614,7 +5866,7 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A35" s="10"/>
       <c r="B35" s="7"/>
       <c r="C35" s="5"/>
@@ -5630,7 +5882,7 @@
       <c r="K35" s="5"/>
       <c r="L35" s="5"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A36" s="10"/>
       <c r="B36" s="7"/>
       <c r="C36" s="5"/>
@@ -5646,7 +5898,7 @@
       <c r="K36" s="5"/>
       <c r="L36" s="5"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A37" s="10"/>
       <c r="B37" s="7"/>
       <c r="C37" s="5"/>
@@ -5662,7 +5914,7 @@
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A38" s="10"/>
       <c r="B38" s="7"/>
       <c r="C38" s="5"/>
@@ -5678,7 +5930,7 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A39" s="10"/>
       <c r="B39" s="7"/>
       <c r="C39" s="5"/>
@@ -5694,7 +5946,7 @@
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A40" s="10"/>
       <c r="B40" s="7"/>
       <c r="C40" s="5"/>
@@ -5710,7 +5962,7 @@
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A41" s="10"/>
       <c r="B41" s="7"/>
       <c r="C41" s="5"/>
@@ -5726,7 +5978,7 @@
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A42" s="10"/>
       <c r="B42" s="7"/>
       <c r="C42" s="5"/>
@@ -5742,7 +5994,7 @@
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A43" s="10"/>
       <c r="B43" s="7"/>
       <c r="C43" s="5"/>
@@ -5758,7 +6010,7 @@
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A44" s="10"/>
       <c r="B44" s="7"/>
       <c r="C44" s="5"/>
@@ -5774,7 +6026,7 @@
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A45" s="10"/>
       <c r="B45" s="7"/>
       <c r="C45" s="5"/>
@@ -5790,7 +6042,7 @@
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A46" s="10"/>
       <c r="B46" s="7"/>
       <c r="C46" s="5"/>
@@ -5806,7 +6058,7 @@
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A47" s="10"/>
       <c r="B47" s="7"/>
       <c r="C47" s="5"/>
@@ -5822,7 +6074,7 @@
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A48" s="10"/>
       <c r="B48" s="7"/>
       <c r="C48" s="5"/>
@@ -5838,7 +6090,7 @@
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A49" s="10"/>
       <c r="B49" s="7"/>
       <c r="C49" s="5"/>
@@ -5854,7 +6106,7 @@
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A50" s="10"/>
       <c r="B50" s="7"/>
       <c r="C50" s="5"/>
@@ -5870,7 +6122,7 @@
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A51" s="10"/>
       <c r="B51" s="7"/>
       <c r="C51" s="5"/>
@@ -5886,7 +6138,7 @@
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A52" s="10"/>
       <c r="B52" s="7">
         <v>45352</v>
@@ -5902,7 +6154,7 @@
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A53" s="10"/>
       <c r="B53" s="7">
         <v>45474</v>
@@ -5926,7 +6178,7 @@
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A54" s="10"/>
       <c r="B54" s="7"/>
       <c r="C54" s="5"/>
@@ -5942,7 +6194,7 @@
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A55" s="10"/>
       <c r="B55" s="7">
         <v>45352</v>
@@ -5966,7 +6218,7 @@
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A56" s="11"/>
       <c r="B56" s="8"/>
       <c r="C56" s="6"/>
@@ -5993,7 +6245,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6414C422-A3C2-4316-8A78-31588DED5AFD}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6003,16 +6255,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="20.4375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.4375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.4140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.4140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.25" customWidth="1"/>
-    <col min="7" max="8" width="10.8125" customWidth="1"/>
+    <col min="7" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="69.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -6041,7 +6293,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>39</v>
       </c>
@@ -6068,7 +6320,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:9" ht="34" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
@@ -6097,7 +6349,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>40</v>
       </c>
@@ -6126,7 +6378,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:9" ht="34" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>41</v>
       </c>
@@ -6155,7 +6407,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>42</v>
       </c>
@@ -6182,7 +6434,7 @@
       </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>43</v>
       </c>
@@ -6207,7 +6459,7 @@
       </c>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:9" ht="34" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>44</v>
       </c>
@@ -6236,7 +6488,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:9" ht="34" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>44</v>
       </c>
